--- a/docs/Тесты.xlsx
+++ b/docs/Тесты.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rufus\Desktop\Repositories\Python\MO_Pt2\NSTU_MO_2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Repositories\! Repo 2.0\NSTU\[6] MO\Opt_methods_2\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5DB211-5630-471A-939D-440386A1B12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724327D0-9CE7-4700-AB8A-3D68041DE76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{098766AF-C197-4C7E-BDEC-25F5D126499E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{098766AF-C197-4C7E-BDEC-25F5D126499E}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="67">
   <si>
     <t>Точность</t>
   </si>
@@ -44,21 +44,6 @@
   </si>
   <si>
     <t>Значение в точке</t>
-  </si>
-  <si>
-    <t>1e-03</t>
-  </si>
-  <si>
-    <t>1e-04</t>
-  </si>
-  <si>
-    <t>1e-05</t>
-  </si>
-  <si>
-    <t>1e-06</t>
-  </si>
-  <si>
-    <t>1e-07</t>
   </si>
   <si>
     <t>x</t>
@@ -157,10 +142,94 @@
     <t>0.01806405]</t>
   </si>
   <si>
-    <t>Н</t>
+    <t>5;4</t>
   </si>
   <si>
-    <t>Б</t>
+    <t>Бро</t>
+  </si>
+  <si>
+    <t>МНС</t>
+  </si>
+  <si>
+    <t>Метод наискорейшего спуска. Функция варианта</t>
+  </si>
+  <si>
+    <t>Метод Бройдена. Функция варианта</t>
+  </si>
+  <si>
+    <t>-3.16370282]</t>
+  </si>
+  <si>
+    <t>[-3.16370282</t>
+  </si>
+  <si>
+    <t>26.07002713]</t>
+  </si>
+  <si>
+    <t>[1.15401454</t>
+  </si>
+  <si>
+    <t>0.53264631]</t>
+  </si>
+  <si>
+    <t>[0.53264631</t>
+  </si>
+  <si>
+    <t>[0.8859661</t>
+  </si>
+  <si>
+    <t>0.05871864]</t>
+  </si>
+  <si>
+    <t>[0.05871864</t>
+  </si>
+  <si>
+    <t>0.65292965]</t>
+  </si>
+  <si>
+    <t>-0.19274053]</t>
+  </si>
+  <si>
+    <t>[-0.19274053</t>
+  </si>
+  <si>
+    <t>0.34156216]</t>
+  </si>
+  <si>
+    <t>-0.01031706]</t>
+  </si>
+  <si>
+    <t>[-0.01031706</t>
+  </si>
+  <si>
+    <t>0.28204399]</t>
+  </si>
+  <si>
+    <t>[5.73401585e-01</t>
+  </si>
+  <si>
+    <t>5.05504054e-04]</t>
+  </si>
+  <si>
+    <t>[5.05504054e-04</t>
+  </si>
+  <si>
+    <t>2.85921801e-01]</t>
+  </si>
+  <si>
+    <t>[1.00000143</t>
+  </si>
+  <si>
+    <t>1.1402451]</t>
+  </si>
+  <si>
+    <t>[1.16878798</t>
+  </si>
+  <si>
+    <t>[0.61239674</t>
+  </si>
+  <si>
+    <t>9;8</t>
   </si>
 </sst>
 </file>
@@ -369,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -377,16 +446,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
@@ -479,24 +542,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -527,16 +572,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -545,7 +581,37 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -557,7 +623,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -583,7 +709,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>52387</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="65" cy="172227"/>
@@ -638,12 +764,12 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>392530</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>4011</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="440698" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -768,7 +894,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -810,6 +936,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -828,12 +955,12 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>143878</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>1003</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="522387" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -964,7 +1091,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -1006,6 +1133,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1024,12 +1152,12 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>229257</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>29889</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3613</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="663900" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -1043,7 +1171,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7668282" y="220389"/>
+              <a:off x="7665326" y="200682"/>
               <a:ext cx="663900" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1160,7 +1288,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -1174,7 +1302,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7668282" y="220389"/>
+              <a:off x="7665326" y="200682"/>
               <a:ext cx="663900" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1202,6 +1330,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1220,12 +1349,12 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>220389</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>28247</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>8540</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="625684" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="TextBox 13">
@@ -1239,7 +1368,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8726214" y="218747"/>
+              <a:off x="8720630" y="205609"/>
               <a:ext cx="625684" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1356,7 +1485,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="TextBox 13">
@@ -1370,7 +1499,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8726214" y="218747"/>
+              <a:off x="8720630" y="205609"/>
               <a:ext cx="625684" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1398,6 +1527,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1416,12 +1546,12 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>303689</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>13138</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="662104" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -1435,7 +1565,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6675914" y="203638"/>
+              <a:off x="6675586" y="197069"/>
               <a:ext cx="662104" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1552,7 +1682,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -1566,7 +1696,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6675914" y="203638"/>
+              <a:off x="6675586" y="197069"/>
               <a:ext cx="662104" cy="172227"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1594,6 +1724,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1612,12 +1743,12 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>392530</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>4011</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="440698" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="TextBox 20">
@@ -1742,7 +1873,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="TextBox 20">
@@ -1784,6 +1915,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1802,12 +1934,12 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>143878</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>1003</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="522387" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="TextBox 21">
@@ -1938,7 +2070,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="TextBox 21">
@@ -1980,6 +2112,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1998,12 +2131,12 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>229257</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>29889</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="663900" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="TextBox 22">
@@ -2134,7 +2267,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="TextBox 22">
@@ -2176,6 +2309,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2194,12 +2328,12 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>220389</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>28247</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="625684" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="24" name="TextBox 23">
@@ -2330,7 +2464,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="24" name="TextBox 23">
@@ -2372,6 +2506,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2390,12 +2525,12 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>303689</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>13138</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="662104" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="25" name="TextBox 24">
@@ -2526,7 +2661,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="25" name="TextBox 24">
@@ -2568,6 +2703,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -4516,6 +4652,2019 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>|𝑥_𝑖−𝑥_(𝑖−1) |</a:t>
+              </a:r>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="TextBox 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DA8FBC7-E25C-4718-B195-0DDF2465BF98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8829115" y="1666034"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392530</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>4011</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="440698" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="48" name="TextBox 47">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC6D6E33-88EC-4DEC-823D-60DA5A15788B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="527001" y="205717"/>
+              <a:ext cx="440698" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>(</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑥</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>,</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑦</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>)</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="48" name="TextBox 47">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC6D6E33-88EC-4DEC-823D-60DA5A15788B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="527001" y="205717"/>
+              <a:ext cx="440698" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(𝑥_𝑖,𝑦_𝑖)</a:t>
+              </a:r>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>143878</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1003</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="522387" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="49" name="TextBox 48">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{836EB1D7-DD8F-4838-A54B-8C84127A5A91}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2340231" y="202709"/>
+              <a:ext cx="522387" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑓</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>(</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑥</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>,</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑦</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>)</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="49" name="TextBox 48">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{836EB1D7-DD8F-4838-A54B-8C84127A5A91}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2340231" y="202709"/>
+              <a:ext cx="522387" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑓(𝑥_𝑖,𝑦_𝑖)</a:t>
+              </a:r>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>229257</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>3613</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="663900" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="50" name="TextBox 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73B5DA7D-58B8-4710-8820-B7A4C30A45F5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7669963" y="205319"/>
+              <a:ext cx="663900" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>|</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑦</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>−</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑦</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>|</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="50" name="TextBox 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73B5DA7D-58B8-4710-8820-B7A4C30A45F5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7669963" y="205319"/>
+              <a:ext cx="663900" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>|𝑦_𝑖−𝑦_(𝑖−1) |</a:t>
+              </a:r>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>220389</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>8540</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="625684" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="51" name="TextBox 50">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D16E0BFA-6FB2-4568-9399-EAEF18B89A30}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8725654" y="210246"/>
+              <a:ext cx="625684" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>|</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑓</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>−</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑓</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>|</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="51" name="TextBox 50">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D16E0BFA-6FB2-4568-9399-EAEF18B89A30}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8725654" y="210246"/>
+              <a:ext cx="625684" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>|𝑓_𝑖−𝑓_(𝑖−1) |</a:t>
+              </a:r>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>303689</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="662104" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="52" name="TextBox 51">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9944E6AB-2859-452E-BD4B-C308FF4A7CD5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6679836" y="201706"/>
+              <a:ext cx="662104" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>|</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑥</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>−</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑥</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>|</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="52" name="TextBox 51">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9944E6AB-2859-452E-BD4B-C308FF4A7CD5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6679836" y="201706"/>
+              <a:ext cx="662104" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>|𝑥_𝑖−𝑥_(𝑖−1) |</a:t>
+              </a:r>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392530</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>4011</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="440698" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="53" name="TextBox 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E286F348-023F-448C-A10C-F11D04F02171}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="527001" y="6727540"/>
+              <a:ext cx="440698" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>(</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑥</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>,</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑦</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>)</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="53" name="TextBox 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E286F348-023F-448C-A10C-F11D04F02171}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="527001" y="6727540"/>
+              <a:ext cx="440698" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(𝑥_𝑖,𝑦_𝑖)</a:t>
+              </a:r>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>143878</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>1003</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="522387" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="54" name="TextBox 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93DFB86A-2858-4DFE-BBC2-6F749B0BDD77}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2340231" y="6724532"/>
+              <a:ext cx="522387" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑓</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>(</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑥</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>,</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑦</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>)</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="54" name="TextBox 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93DFB86A-2858-4DFE-BBC2-6F749B0BDD77}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2340231" y="6724532"/>
+              <a:ext cx="522387" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑓(𝑥_𝑖,𝑦_𝑖)</a:t>
+              </a:r>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>229257</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>29889</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="663900" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55" name="TextBox 54">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E5925A1-48D8-4600-B830-E6CE8AA5E143}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7669963" y="6753418"/>
+              <a:ext cx="663900" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>|</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑦</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>−</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑦</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>|</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55" name="TextBox 54">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E5925A1-48D8-4600-B830-E6CE8AA5E143}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7669963" y="6753418"/>
+              <a:ext cx="663900" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>|𝑦_𝑖−𝑦_(𝑖−1) |</a:t>
+              </a:r>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>220389</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>28247</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="625684" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="56" name="TextBox 55">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5CFA6D6-4528-4547-B4AC-14F7773EA78C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8725654" y="6751776"/>
+              <a:ext cx="625684" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>|</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑓</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>−</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑓</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>|</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="56" name="TextBox 55">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5CFA6D6-4528-4547-B4AC-14F7773EA78C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8725654" y="6751776"/>
+              <a:ext cx="625684" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>|𝑓_𝑖−𝑓_(𝑖−1) |</a:t>
+              </a:r>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>303689</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>13138</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="662104" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="57" name="TextBox 56">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A2D1A10-A667-493C-B0E7-351AD1CF2C13}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6679836" y="6736667"/>
+              <a:ext cx="662104" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>|</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑥</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>−</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑥</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>|</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ru-RU" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="57" name="TextBox 56">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A2D1A10-A667-493C-B0E7-351AD1CF2C13}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6679836" y="6736667"/>
+              <a:ext cx="662104" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -4830,615 +6979,619 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC9AB0E-F2EB-4B0E-9E38-0A1BC4764938}">
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="10"/>
+    <col min="1" max="1" width="9.140625" style="8"/>
     <col min="2" max="2" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16.88671875" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.109375" style="2"/>
+    <col min="3" max="3" width="19.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44" t="s">
+      <c r="E1" s="57"/>
+      <c r="F1" s="57" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1"/>
-      <c r="H1" s="1">
+      <c r="H1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="51"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2">
-        <v>4</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="45"/>
+      <c r="E2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="58"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="77">
+        <v>1E-3</v>
+      </c>
+      <c r="B3" s="3">
         <v>5</v>
       </c>
-      <c r="B3" s="4">
-        <v>7</v>
-      </c>
-      <c r="C3" s="24">
-        <v>586</v>
-      </c>
-      <c r="D3" s="27">
-        <v>1.00424307</v>
-      </c>
-      <c r="E3" s="21">
-        <v>1.0042647</v>
-      </c>
-      <c r="F3" s="21">
-        <v>1.8050449799999999E-5</v>
+      <c r="C3" s="22">
+        <v>332</v>
+      </c>
+      <c r="D3" s="25">
+        <v>1.0003155100000001</v>
+      </c>
+      <c r="E3" s="19">
+        <v>1.0003171099999999</v>
+      </c>
+      <c r="F3" s="19">
+        <v>9.9803090000000006E-8</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="77">
+        <v>1E-4</v>
+      </c>
+      <c r="B4" s="3">
+        <v>5</v>
+      </c>
+      <c r="C4" s="22">
+        <v>332</v>
+      </c>
+      <c r="D4" s="25">
+        <v>1.0003155100000001</v>
+      </c>
+      <c r="E4" s="19">
+        <v>1.0003171099999999</v>
+      </c>
+      <c r="F4" s="19">
+        <v>9.9803090000000006E-8</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="49"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="77">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="B5" s="3">
         <v>6</v>
       </c>
-      <c r="B4" s="4">
-        <v>8</v>
-      </c>
-      <c r="C4" s="24">
-        <v>672</v>
-      </c>
-      <c r="D4" s="27">
-        <v>1.00051063</v>
-      </c>
-      <c r="E4" s="21">
-        <v>1.00038297</v>
-      </c>
-      <c r="F4" s="21">
-        <v>1.8904964899999999E-6</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="4">
-        <v>9</v>
-      </c>
-      <c r="C5" s="24">
-        <v>754</v>
-      </c>
-      <c r="D5" s="27">
-        <v>1.00044439</v>
-      </c>
-      <c r="E5" s="21">
-        <v>1.0004466599999999</v>
-      </c>
-      <c r="F5" s="21">
-        <v>1.98000096E-7</v>
+      <c r="C5" s="22">
+        <v>402</v>
+      </c>
+      <c r="D5" s="25">
+        <v>1.0000306400000001</v>
+      </c>
+      <c r="E5" s="19">
+        <v>1.0000308</v>
+      </c>
+      <c r="F5" s="19">
+        <v>9.4145600399999991E-10</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="4">
-        <v>10</v>
-      </c>
-      <c r="C6" s="24">
-        <v>840</v>
-      </c>
-      <c r="D6" s="27">
-        <v>1.00005495</v>
-      </c>
-      <c r="E6" s="21">
-        <v>1.0000414099999999</v>
-      </c>
-      <c r="F6" s="21">
-        <v>2.1351759499999999E-8</v>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="77">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="B6" s="3">
+        <v>6</v>
+      </c>
+      <c r="C6" s="22">
+        <v>402</v>
+      </c>
+      <c r="D6" s="25">
+        <v>1.0000306400000001</v>
+      </c>
+      <c r="E6" s="19">
+        <v>1.0000308</v>
+      </c>
+      <c r="F6" s="19">
+        <v>9.4145600399999991E-10</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7">
-        <v>11</v>
-      </c>
-      <c r="C7" s="8">
-        <v>922</v>
-      </c>
-      <c r="D7" s="28">
-        <v>1.0000479200000001</v>
-      </c>
-      <c r="E7" s="19">
-        <v>1.0000481699999999</v>
-      </c>
-      <c r="F7" s="19">
-        <v>2.3025232300000001E-9</v>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="78">
+        <v>9.9999999999999995E-8</v>
+      </c>
+      <c r="B7" s="5">
+        <v>6</v>
+      </c>
+      <c r="C7" s="6">
+        <v>402</v>
+      </c>
+      <c r="D7" s="26">
+        <v>1.0000306400000001</v>
+      </c>
+      <c r="E7" s="17">
+        <v>1.0000308</v>
+      </c>
+      <c r="F7" s="17">
+        <v>9.4145600399999991E-10</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1"/>
+    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="76"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="37" t="s">
+    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="43" t="s">
+      <c r="D9" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44" t="s">
+      <c r="E9" s="57"/>
+      <c r="F9" s="57" t="s">
         <v>4</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="J9" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="38"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="11" t="s">
+      <c r="H9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="51"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="58"/>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="77">
+        <v>1E-3</v>
+      </c>
+      <c r="B11" s="3">
+        <v>7</v>
+      </c>
+      <c r="C11" s="22">
+        <v>414</v>
+      </c>
+      <c r="D11" s="25">
+        <v>1.0035688599999999</v>
+      </c>
+      <c r="E11" s="19">
+        <v>1.0035870499999999</v>
+      </c>
+      <c r="F11" s="19">
+        <v>1.2769830499999999E-5</v>
+      </c>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="77">
+        <v>1E-4</v>
+      </c>
+      <c r="B12" s="3">
+        <v>8</v>
+      </c>
+      <c r="C12" s="22">
+        <v>484</v>
+      </c>
+      <c r="D12" s="25">
+        <v>1.0004295000000001</v>
+      </c>
+      <c r="E12" s="19">
+        <v>1.00032213</v>
+      </c>
+      <c r="F12" s="19">
+        <v>1.3374712199999999E-6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="77">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="B13" s="3">
+        <v>9</v>
+      </c>
+      <c r="C13" s="22">
+        <v>535</v>
+      </c>
+      <c r="D13" s="25">
+        <v>1.00037379</v>
+      </c>
+      <c r="E13" s="19">
+        <v>1.0003757</v>
+      </c>
+      <c r="F13" s="19">
+        <v>1.4008306299999999E-7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="77">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="C14" s="22">
+        <v>605</v>
+      </c>
+      <c r="D14" s="25">
+        <v>1.0000426499999999</v>
+      </c>
+      <c r="E14" s="19">
+        <v>1.00003168</v>
+      </c>
+      <c r="F14" s="19">
+        <v>1.38527563E-8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="78">
+        <v>9.9999999999999995E-8</v>
+      </c>
+      <c r="B15" s="5">
         <v>11</v>
       </c>
-      <c r="F10" s="45"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="C15" s="6">
+        <v>656</v>
+      </c>
+      <c r="D15" s="26">
+        <v>1.0000369600000001</v>
+      </c>
+      <c r="E15" s="17">
+        <v>1.00003715</v>
+      </c>
+      <c r="F15" s="17">
+        <v>1.36986606E-9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="51"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="4">
+      <c r="E18" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="58"/>
+      <c r="H18" s="49"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="77">
+        <v>1E-3</v>
+      </c>
+      <c r="B19" s="3">
+        <v>7</v>
+      </c>
+      <c r="C19" s="22">
+        <v>472</v>
+      </c>
+      <c r="D19" s="25">
+        <v>1.0109265700000001</v>
+      </c>
+      <c r="E19" s="19">
+        <v>1.01098329</v>
+      </c>
+      <c r="F19" s="19">
+        <v>1.19711669E-4</v>
+      </c>
+      <c r="H19" s="49"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="77">
+        <v>1E-4</v>
+      </c>
+      <c r="B20" s="3">
+        <v>9</v>
+      </c>
+      <c r="C20" s="22">
+        <v>612</v>
+      </c>
+      <c r="D20" s="25">
+        <v>1.0012398600000001</v>
+      </c>
+      <c r="E20" s="19">
+        <v>1.0012463</v>
+      </c>
+      <c r="F20" s="19">
+        <v>1.54139691E-6</v>
+      </c>
+      <c r="H20" s="49"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="77">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="B21" s="3">
+        <v>10</v>
+      </c>
+      <c r="C21" s="22">
+        <v>682</v>
+      </c>
+      <c r="D21" s="25">
+        <v>1.0004176499999999</v>
+      </c>
+      <c r="E21" s="19">
+        <v>1.0004198200000001</v>
+      </c>
+      <c r="F21" s="19">
+        <v>1.7490517200000001E-7</v>
+      </c>
+      <c r="H21" s="49"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="77">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="B22" s="3">
+        <v>11</v>
+      </c>
+      <c r="C22" s="22">
+        <v>752</v>
+      </c>
+      <c r="D22" s="25">
+        <v>1.0001406900000001</v>
+      </c>
+      <c r="E22" s="19">
+        <v>1.0001414200000001</v>
+      </c>
+      <c r="F22" s="19">
+        <v>1.9846782599999999E-8</v>
+      </c>
+      <c r="H22" s="49"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="78">
+        <v>9.9999999999999995E-8</v>
+      </c>
+      <c r="B23" s="5">
+        <v>12</v>
+      </c>
+      <c r="C23" s="6">
+        <v>822</v>
+      </c>
+      <c r="D23" s="26">
+        <v>1.00004739</v>
+      </c>
+      <c r="E23" s="17">
+        <v>1.00004764</v>
+      </c>
+      <c r="F23" s="17">
+        <v>2.2520459600000001E-9</v>
+      </c>
+      <c r="H23" s="49"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H24" s="49"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="51"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="24">
-        <v>427</v>
-      </c>
-      <c r="D11" s="27">
-        <v>1.0004447000000001</v>
-      </c>
-      <c r="E11" s="21">
-        <v>1.00044697</v>
-      </c>
-      <c r="F11" s="21">
-        <v>1.9827172199999999E-7</v>
-      </c>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="E26" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="4">
-        <v>5</v>
-      </c>
-      <c r="C12" s="24">
-        <v>427</v>
-      </c>
-      <c r="D12" s="27">
-        <v>1.0004447000000001</v>
-      </c>
-      <c r="E12" s="21">
-        <v>1.00044697</v>
-      </c>
-      <c r="F12" s="21">
-        <v>1.9827172199999999E-7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="4">
-        <v>6</v>
-      </c>
-      <c r="C13" s="24">
-        <v>513</v>
-      </c>
-      <c r="D13" s="27">
-        <v>1.00004705</v>
-      </c>
-      <c r="E13" s="21">
-        <v>1.0000472899999999</v>
-      </c>
-      <c r="F13" s="21">
-        <v>2.21935692E-9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="4">
-        <v>6</v>
-      </c>
-      <c r="C14" s="24">
-        <v>513</v>
-      </c>
-      <c r="D14" s="27">
-        <v>1.00004705</v>
-      </c>
-      <c r="E14" s="21">
-        <v>1.0000472899999999</v>
-      </c>
-      <c r="F14" s="21">
-        <v>2.21935692E-9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7">
-        <v>7</v>
-      </c>
-      <c r="C15" s="8">
-        <v>599</v>
-      </c>
-      <c r="D15" s="28">
-        <v>1.0000049799999999</v>
-      </c>
-      <c r="E15" s="19">
-        <v>1.000005</v>
-      </c>
-      <c r="F15" s="19">
-        <v>2.4841118000000001E-11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
-    </row>
-    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="2">
-        <v>9</v>
-      </c>
-      <c r="I17" s="2">
-        <v>8</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="38"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="45"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="4">
-        <v>11</v>
-      </c>
-      <c r="C19" s="24">
-        <v>922</v>
-      </c>
-      <c r="D19" s="27">
-        <v>1.01034234</v>
-      </c>
-      <c r="E19" s="21">
-        <v>1.0103957699999999</v>
-      </c>
-      <c r="F19" s="21">
-        <v>1.07249496E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="4">
+      <c r="F26" s="58"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="77">
+        <v>1E-3</v>
+      </c>
+      <c r="B27" s="3">
         <v>12</v>
       </c>
-      <c r="C20" s="24">
-        <v>1008</v>
-      </c>
-      <c r="D20" s="27">
-        <v>1.0030845500000001</v>
-      </c>
-      <c r="E20" s="21">
-        <v>1.00263737</v>
-      </c>
-      <c r="F20" s="21">
-        <v>2.9511907099999999E-5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="4">
+      <c r="C27" s="22">
+        <v>726</v>
+      </c>
+      <c r="D27" s="25">
+        <v>1.0121405299999999</v>
+      </c>
+      <c r="E27" s="19">
+        <v>1.0106229799999999</v>
+      </c>
+      <c r="F27" s="19">
+        <v>3.7768810200000002E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="77">
+        <v>1E-4</v>
+      </c>
+      <c r="B28" s="3">
         <v>14</v>
       </c>
-      <c r="C21" s="24">
-        <v>1176</v>
-      </c>
-      <c r="D21" s="27">
-        <v>1.00085245</v>
-      </c>
-      <c r="E21" s="21">
-        <v>1.0007292299999999</v>
-      </c>
-      <c r="F21" s="21">
-        <v>2.2447934100000001E-6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="4">
+      <c r="C28" s="22">
+        <v>847</v>
+      </c>
+      <c r="D28" s="25">
+        <v>1.0041010500000001</v>
+      </c>
+      <c r="E28" s="19">
+        <v>1.00358546</v>
+      </c>
+      <c r="F28" s="19">
+        <v>4.3401911799999998E-5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="77">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="B29" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="24">
-        <v>1344</v>
-      </c>
-      <c r="D22" s="27">
-        <v>1.00023459</v>
-      </c>
-      <c r="E22" s="21">
-        <v>1.00020058</v>
-      </c>
-      <c r="F22" s="21">
-        <v>1.7072499800000001E-7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="7">
-        <v>18</v>
-      </c>
-      <c r="C23" s="8">
-        <v>1512</v>
-      </c>
-      <c r="D23" s="28">
-        <v>1.0000648000000001</v>
-      </c>
-      <c r="E23" s="19">
-        <v>1.00005543</v>
-      </c>
-      <c r="F23" s="19">
-        <v>1.2977938999999999E-8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="2"/>
-    </row>
-    <row r="25" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="38"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="45"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="4">
-        <v>7</v>
-      </c>
-      <c r="C27" s="24">
-        <v>599</v>
-      </c>
-      <c r="D27" s="27">
-        <v>1.0028499099999999</v>
-      </c>
-      <c r="E27" s="21">
-        <v>1.0028646400000001</v>
-      </c>
-      <c r="F27" s="21">
-        <v>8.1436982300000002E-6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="4">
-        <v>7</v>
-      </c>
-      <c r="C28" s="24">
-        <v>599</v>
-      </c>
-      <c r="D28" s="27">
-        <v>1.0028499099999999</v>
-      </c>
-      <c r="E28" s="21">
-        <v>1.0028646400000001</v>
-      </c>
-      <c r="F28" s="21">
-        <v>8.1436982300000002E-6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="4">
-        <v>8</v>
-      </c>
-      <c r="C29" s="24">
-        <v>685</v>
-      </c>
-      <c r="D29" s="27">
-        <v>1.00078588</v>
-      </c>
-      <c r="E29" s="21">
-        <v>1.00078994</v>
-      </c>
-      <c r="F29" s="21">
-        <v>6.1925179099999997E-7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="4">
-        <v>9</v>
-      </c>
-      <c r="C30" s="24">
-        <v>771</v>
-      </c>
-      <c r="D30" s="27">
-        <v>1.0002167099999999</v>
-      </c>
-      <c r="E30" s="21">
-        <v>1.00021783</v>
-      </c>
-      <c r="F30" s="21">
-        <v>4.7088173300000002E-8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="7">
-        <v>10</v>
-      </c>
-      <c r="C31" s="8">
-        <v>857</v>
-      </c>
-      <c r="D31" s="28">
-        <v>1.0000597600000001</v>
-      </c>
-      <c r="E31" s="19">
-        <v>1.00006007</v>
-      </c>
-      <c r="F31" s="19">
-        <v>3.5806100200000002E-9</v>
+      <c r="C29" s="22">
+        <v>968</v>
+      </c>
+      <c r="D29" s="25">
+        <v>1.0013950899999999</v>
+      </c>
+      <c r="E29" s="19">
+        <v>1.0012207099999999</v>
+      </c>
+      <c r="F29" s="19">
+        <v>4.9874028300000002E-6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="77">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="B30" s="3">
+        <v>19</v>
+      </c>
+      <c r="C30" s="22">
+        <v>1140</v>
+      </c>
+      <c r="D30" s="25">
+        <v>1.0004392900000001</v>
+      </c>
+      <c r="E30" s="19">
+        <v>1.00044157</v>
+      </c>
+      <c r="F30" s="19">
+        <v>1.9349543200000001E-7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="78">
+        <v>9.9999999999999995E-8</v>
+      </c>
+      <c r="B31" s="5">
+        <v>21</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1261</v>
+      </c>
+      <c r="D31" s="26">
+        <v>1.00014946</v>
+      </c>
+      <c r="E31" s="17">
+        <v>1.00015024</v>
+      </c>
+      <c r="F31" s="17">
+        <v>2.2399925800000002E-8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="F17:F18"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5447,1016 +7600,1067 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C07E64-7C14-49F0-845C-FB0F44D8A6BF}">
-  <dimension ref="A1:U59"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U80"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.44140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="18" customWidth="1"/>
-    <col min="5" max="6" width="16" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="16" style="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" style="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.44140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="2.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="16.42578125" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="16.42578125" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="63"/>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="61"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="63"/>
+      <c r="G2" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="63"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
+    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="38">
+        <v>1</v>
+      </c>
+      <c r="B3" s="27">
+        <v>4.4811533099999998</v>
+      </c>
+      <c r="C3" s="12">
+        <v>4.4988910500000001</v>
+      </c>
+      <c r="D3" s="15">
+        <v>12.1498911</v>
+      </c>
+      <c r="E3" s="27">
+        <v>-208.00001700000001</v>
+      </c>
+      <c r="F3" s="12">
+        <v>200.00001700000001</v>
+      </c>
+      <c r="G3" s="15">
+        <v>2.4944550499999998E-3</v>
+      </c>
+      <c r="H3" s="11">
+        <v>-0.51884669400000005</v>
+      </c>
+      <c r="I3" s="15">
+        <v>0.498891052</v>
+      </c>
+      <c r="J3" s="11">
+        <v>-103.850109</v>
+      </c>
+      <c r="K3" s="15">
+        <v>1.58842642</v>
+      </c>
+      <c r="L3" s="27">
+        <v>3.4147582500000002</v>
+      </c>
+      <c r="M3" s="12">
+        <v>3.54754981</v>
+      </c>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
+    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="48">
+        <v>2</v>
+      </c>
+      <c r="B4" s="34">
+        <v>1.39736533</v>
+      </c>
+      <c r="C4" s="10">
+        <v>1.2951821400000001</v>
+      </c>
+      <c r="D4" s="24">
+        <v>1.2020396099999999</v>
+      </c>
+      <c r="E4" s="34">
+        <v>-3.4147582500000002</v>
+      </c>
+      <c r="F4" s="10">
+        <v>-3.54754981</v>
+      </c>
+      <c r="G4" s="24">
+        <v>0.903076514</v>
+      </c>
+      <c r="H4" s="9">
+        <v>-3.0837879799999999</v>
+      </c>
+      <c r="I4" s="24">
+        <v>-3.20370891</v>
+      </c>
+      <c r="J4" s="9">
+        <v>-10.947851500000001</v>
+      </c>
+      <c r="K4" s="24">
+        <v>3.0845898699999998</v>
+      </c>
+      <c r="L4" s="34">
+        <v>21.231370200000001</v>
+      </c>
+      <c r="M4" s="10">
+        <v>-20.436639499999998</v>
+      </c>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
+    <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="38">
+        <v>3</v>
+      </c>
+      <c r="B5" s="27">
+        <v>1.3444046300000001</v>
+      </c>
+      <c r="C5" s="12">
+        <v>1.3461604199999999</v>
+      </c>
+      <c r="D5" s="15">
+        <v>0.11892282699999999</v>
+      </c>
+      <c r="E5" s="27">
+        <v>-21.231370200000001</v>
+      </c>
+      <c r="F5" s="12">
+        <v>20.436639499999998</v>
+      </c>
+      <c r="G5" s="15">
+        <v>2.4944550499999998E-3</v>
+      </c>
+      <c r="H5" s="11">
+        <v>-5.2960698700000003E-2</v>
+      </c>
+      <c r="I5" s="15">
+        <v>5.0978278699999997E-2</v>
+      </c>
+      <c r="J5" s="11">
+        <v>-1.0831167900000001</v>
+      </c>
+      <c r="K5" s="15">
+        <v>1.5892143599999999</v>
+      </c>
+      <c r="L5" s="27">
+        <v>0.33765168400000001</v>
+      </c>
+      <c r="M5" s="12">
+        <v>0.35115781099999999</v>
+      </c>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
+    <row r="6" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="48">
+        <v>4</v>
+      </c>
+      <c r="B6" s="34">
+        <v>1.0414499800000001</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1.03108753</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1.24561394E-2</v>
+      </c>
+      <c r="E6" s="34">
+        <v>-0.33765168400000001</v>
+      </c>
+      <c r="F6" s="10">
+        <v>-0.35115781099999999</v>
+      </c>
+      <c r="G6" s="24">
+        <v>0.89724014900000004</v>
+      </c>
+      <c r="H6" s="9">
+        <v>-0.30295464799999999</v>
+      </c>
+      <c r="I6" s="24">
+        <v>-0.31507288700000002</v>
+      </c>
+      <c r="J6" s="9">
+        <v>-0.106466688</v>
+      </c>
+      <c r="K6" s="24">
+        <v>3.1169873899999998</v>
+      </c>
+      <c r="L6" s="34">
+        <v>2.15539039</v>
+      </c>
+      <c r="M6" s="10">
+        <v>-2.0724902200000002</v>
+      </c>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
+    <row r="7" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="38">
+        <v>5</v>
+      </c>
+      <c r="B7" s="27">
+        <v>1.0360734599999999</v>
+      </c>
+      <c r="C7" s="12">
+        <v>1.03625726</v>
+      </c>
+      <c r="D7" s="15">
+        <v>1.3046727199999999E-3</v>
+      </c>
+      <c r="E7" s="27">
+        <v>-2.15539039</v>
+      </c>
+      <c r="F7" s="12">
+        <v>2.0724902200000002</v>
+      </c>
+      <c r="G7" s="15">
+        <v>2.4944550499999998E-3</v>
+      </c>
+      <c r="H7" s="11">
+        <v>-5.3765244399999997E-3</v>
+      </c>
+      <c r="I7" s="15">
+        <v>5.1697336999999999E-3</v>
+      </c>
+      <c r="J7" s="11">
+        <v>-1.1151466699999999E-2</v>
+      </c>
+      <c r="K7" s="15">
+        <v>1.59031309</v>
+      </c>
+      <c r="L7" s="27">
+        <v>3.5385534099999998E-2</v>
+      </c>
+      <c r="M7" s="12">
+        <v>3.6761584E-2</v>
+      </c>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="60" t="s">
+    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="48">
+        <v>6</v>
+      </c>
+      <c r="B8" s="34">
+        <v>1.0041176599999999</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1.0030587900000001</v>
+      </c>
+      <c r="D8" s="24">
+        <v>1.29075483E-4</v>
+      </c>
+      <c r="E8" s="34">
+        <v>-3.5385534099999998E-2</v>
+      </c>
+      <c r="F8" s="10">
+        <v>-3.6761584E-2</v>
+      </c>
+      <c r="G8" s="24">
+        <v>0.90307517000000004</v>
+      </c>
+      <c r="H8" s="9">
+        <v>-3.1955797299999998E-2</v>
+      </c>
+      <c r="I8" s="24">
+        <v>-3.3198473700000002E-2</v>
+      </c>
+      <c r="J8" s="9">
+        <v>-1.1755972399999999E-3</v>
+      </c>
+      <c r="K8" s="24">
+        <v>3.1219945899999999</v>
+      </c>
+      <c r="L8" s="34">
+        <v>0.22000925099999999</v>
+      </c>
+      <c r="M8" s="10">
+        <v>-0.21177373299999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="39">
+        <v>7</v>
+      </c>
+      <c r="B9" s="28">
+        <v>1.0035688599999999</v>
+      </c>
+      <c r="C9" s="14">
+        <v>1.0035870499999999</v>
+      </c>
+      <c r="D9" s="21">
+        <v>1.2769830499999999E-5</v>
+      </c>
+      <c r="E9" s="28">
+        <v>-0.22000925099999999</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0.21177373299999999</v>
+      </c>
+      <c r="G9" s="21">
+        <v>2.4944550499999998E-3</v>
+      </c>
+      <c r="H9" s="13">
+        <v>-5.4880318799999995E-4</v>
+      </c>
+      <c r="I9" s="21">
+        <v>5.28260058E-4</v>
+      </c>
+      <c r="J9" s="13">
+        <v>-1.16305652E-4</v>
+      </c>
+      <c r="K9" s="21">
+        <v>1.5898582299999999</v>
+      </c>
+      <c r="L9" s="28">
+        <v>3.4989776900000002E-3</v>
+      </c>
+      <c r="M9" s="14">
+        <v>3.6389343900000001E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="60"/>
+      <c r="M11" s="61"/>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="62"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="63"/>
+      <c r="G12" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="61"/>
-      <c r="M9" s="62"/>
-    </row>
-    <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="58"/>
-      <c r="G10" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="M10" s="58"/>
-    </row>
-    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="20">
+      <c r="M12" s="63"/>
+    </row>
+    <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18">
         <v>1</v>
       </c>
-      <c r="B11" s="29">
-        <v>4.4811460500000004</v>
-      </c>
-      <c r="C11" s="14">
-        <v>4.4988980300000003</v>
-      </c>
-      <c r="D11" s="17">
-        <v>12.1498911</v>
-      </c>
-      <c r="E11" s="29">
-        <v>-208.00001700000001</v>
-      </c>
-      <c r="F11" s="14">
-        <v>200.00001700000001</v>
-      </c>
-      <c r="G11" s="17">
-        <v>2.4944899300000001E-3</v>
-      </c>
-      <c r="H11" s="13">
-        <v>-0.51885394799999995</v>
-      </c>
-      <c r="I11" s="17">
-        <v>0.49889802700000002</v>
-      </c>
-      <c r="J11" s="13">
-        <v>-103.850109</v>
-      </c>
-      <c r="K11" s="17">
-        <v>1.5884248400000001</v>
-      </c>
-      <c r="L11" s="29">
-        <v>3.4118965399999999</v>
-      </c>
-      <c r="M11" s="14">
-        <v>3.5503955299999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="25">
+      <c r="B13" s="27">
+        <v>2.0710685099999999</v>
+      </c>
+      <c r="C13" s="12">
+        <v>4.2928375000000001</v>
+      </c>
+      <c r="D13" s="15">
+        <v>1.1484216700000001</v>
+      </c>
+      <c r="E13" s="27">
+        <v>-42008.010499999997</v>
+      </c>
+      <c r="F13" s="12">
+        <v>4200.00288</v>
+      </c>
+      <c r="G13" s="15">
+        <v>6.9723165900000006E-5</v>
+      </c>
+      <c r="H13" s="11">
+        <v>-2.9289314900000001</v>
+      </c>
+      <c r="I13" s="15">
+        <v>0.292837497</v>
+      </c>
+      <c r="J13" s="11">
+        <v>-44114.851600000002</v>
+      </c>
+      <c r="K13" s="15">
+        <v>1.9206537100000001</v>
+      </c>
+      <c r="L13" s="27">
+        <v>-0.76788308999999999</v>
+      </c>
+      <c r="M13" s="12">
+        <v>0.70254135799999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="23">
         <v>2</v>
       </c>
-      <c r="B12" s="36">
-        <v>1.43060436</v>
-      </c>
-      <c r="C12" s="12">
-        <v>1.3245258099999999</v>
-      </c>
-      <c r="D12" s="26">
-        <v>1.31068601</v>
-      </c>
-      <c r="E12" s="36">
-        <v>-3.4118965399999999</v>
-      </c>
-      <c r="F12" s="12">
-        <v>-3.5503955299999999</v>
-      </c>
-      <c r="G12" s="26">
-        <v>0.89408973999999997</v>
-      </c>
-      <c r="H12" s="11">
-        <v>-3.0505416900000002</v>
-      </c>
-      <c r="I12" s="26">
-        <v>-3.17437222</v>
-      </c>
-      <c r="J12" s="11">
-        <v>-10.839205099999999</v>
-      </c>
-      <c r="K12" s="26">
-        <v>3.0832193600000002</v>
-      </c>
-      <c r="L12" s="36">
-        <v>22.076920699999999</v>
-      </c>
-      <c r="M12" s="12">
-        <v>-21.215711899999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="20">
+      <c r="B14" s="34">
+        <v>2.0713442299999998</v>
+      </c>
+      <c r="C14" s="10">
+        <v>4.2925852400000002</v>
+      </c>
+      <c r="D14" s="24">
+        <v>1.1482271900000001</v>
+      </c>
+      <c r="E14" s="34">
+        <v>0.76788308999999999</v>
+      </c>
+      <c r="F14" s="10">
+        <v>-0.70254135799999995</v>
+      </c>
+      <c r="G14" s="24">
+        <v>3.59060426E-4</v>
+      </c>
+      <c r="H14" s="9">
+        <v>2.7571642999999998E-4</v>
+      </c>
+      <c r="I14" s="24">
+        <v>-2.5225479899999999E-4</v>
+      </c>
+      <c r="J14" s="9">
+        <v>-1.9448398500000001E-4</v>
+      </c>
+      <c r="K14" s="24">
+        <v>1.8622040500000001</v>
+      </c>
+      <c r="L14" s="34">
+        <v>0.38758196700000003</v>
+      </c>
+      <c r="M14" s="10">
+        <v>0.42366399300000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="60"/>
+      <c r="M16" s="61"/>
+    </row>
+    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="62"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="63"/>
+      <c r="G17" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="L17" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="63"/>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="38">
+        <v>1</v>
+      </c>
+      <c r="B18" s="43">
+        <v>2.9999991100000001</v>
+      </c>
+      <c r="C18" s="42">
+        <v>1.93903965</v>
+      </c>
+      <c r="D18" s="40">
+        <v>-2.45849421</v>
+      </c>
+      <c r="E18" s="43">
+        <v>-5.5511151200000002E-8</v>
+      </c>
+      <c r="F18" s="42">
+        <v>0.245254372</v>
+      </c>
+      <c r="G18" s="40">
+        <v>16.0610374</v>
+      </c>
+      <c r="H18" s="45">
+        <v>-8.91566677E-7</v>
+      </c>
+      <c r="I18" s="40">
+        <v>3.9390396499999998</v>
+      </c>
+      <c r="J18" s="45">
+        <v>-2.0906145899999999</v>
+      </c>
+      <c r="K18" s="40">
+        <v>0.99699381600000003</v>
+      </c>
+      <c r="L18" s="43">
+        <v>0.77591000300000001</v>
+      </c>
+      <c r="M18" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="48">
+        <v>2</v>
+      </c>
+      <c r="B19" s="46">
+        <v>2.6388842499999998</v>
+      </c>
+      <c r="C19" s="47">
+        <v>1.93903965</v>
+      </c>
+      <c r="D19" s="24">
+        <v>-2.5951024</v>
+      </c>
+      <c r="E19" s="46">
+        <v>-0.77591000300000001</v>
+      </c>
+      <c r="F19" s="47">
+        <v>0</v>
+      </c>
+      <c r="G19" s="24">
+        <v>0.46540817499999998</v>
+      </c>
+      <c r="H19" s="9">
+        <v>-0.36111485799999998</v>
+      </c>
+      <c r="I19" s="24">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9">
+        <v>-0.13660819299999999</v>
+      </c>
+      <c r="K19" s="24">
+        <v>2.5078938000000002</v>
+      </c>
+      <c r="L19" s="46">
+        <v>0</v>
+      </c>
+      <c r="M19" s="47">
+        <v>-5.3301363300000001E-2</v>
+      </c>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="48">
         <v>3</v>
       </c>
-      <c r="B13" s="29">
-        <v>1.3755337000000001</v>
-      </c>
-      <c r="C13" s="14">
-        <v>1.37744819</v>
-      </c>
-      <c r="D13" s="17">
-        <v>0.141392088</v>
-      </c>
-      <c r="E13" s="29">
-        <v>-22.076920699999999</v>
-      </c>
-      <c r="F13" s="14">
-        <v>21.215711899999999</v>
-      </c>
-      <c r="G13" s="17">
-        <v>2.4944899300000001E-3</v>
-      </c>
-      <c r="H13" s="13">
-        <v>-5.5070656400000001E-2</v>
-      </c>
-      <c r="I13" s="17">
-        <v>5.2922379499999998E-2</v>
-      </c>
-      <c r="J13" s="13">
-        <v>-1.1692939200000001</v>
-      </c>
-      <c r="K13" s="17">
-        <v>1.58999102</v>
-      </c>
-      <c r="L13" s="29">
-        <v>0.36817049400000001</v>
-      </c>
-      <c r="M13" s="14">
-        <v>0.382897131</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="25">
-        <v>4</v>
-      </c>
-      <c r="B14" s="36">
-        <v>1.0451950299999999</v>
-      </c>
-      <c r="C14" s="12">
-        <v>1.03389613</v>
-      </c>
-      <c r="D14" s="26">
-        <v>1.48090993E-2</v>
-      </c>
-      <c r="E14" s="36">
-        <v>-0.36817049400000001</v>
-      </c>
-      <c r="F14" s="12">
-        <v>-0.382897131</v>
-      </c>
-      <c r="G14" s="26">
-        <v>0.89724375700000003</v>
-      </c>
-      <c r="H14" s="11">
-        <v>-0.33033867700000002</v>
-      </c>
-      <c r="I14" s="26">
-        <v>-0.34355205999999999</v>
-      </c>
-      <c r="J14" s="11">
-        <v>-0.12658298900000001</v>
-      </c>
-      <c r="K14" s="26">
-        <v>3.1165530800000001</v>
-      </c>
-      <c r="L14" s="36">
-        <v>2.3501698800000002</v>
-      </c>
-      <c r="M14" s="12">
-        <v>-2.2597796200000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="20">
-        <v>5</v>
-      </c>
-      <c r="B15" s="29">
-        <v>1.0393325499999999</v>
-      </c>
-      <c r="C15" s="14">
-        <v>1.0395331299999999</v>
-      </c>
-      <c r="D15" s="17">
-        <v>1.5510726600000001E-3</v>
-      </c>
-      <c r="E15" s="29">
-        <v>-2.3501698800000002</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2.2597796200000002</v>
-      </c>
-      <c r="G15" s="17">
-        <v>2.4944899300000001E-3</v>
-      </c>
-      <c r="H15" s="13">
-        <v>-5.8624751000000003E-3</v>
-      </c>
-      <c r="I15" s="17">
-        <v>5.6369975100000001E-3</v>
-      </c>
-      <c r="J15" s="13">
-        <v>-1.32580266E-2</v>
-      </c>
-      <c r="K15" s="17">
-        <v>1.59030498</v>
-      </c>
-      <c r="L15" s="29">
-        <v>3.8550219400000002E-2</v>
-      </c>
-      <c r="M15" s="14">
-        <v>4.0115091399999997E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="25">
-        <v>6</v>
-      </c>
-      <c r="B16" s="36">
-        <v>1.0048653000000001</v>
-      </c>
-      <c r="C16" s="12">
-        <v>1.0036667500000001</v>
-      </c>
-      <c r="D16" s="26">
-        <v>1.6732497899999999E-4</v>
-      </c>
-      <c r="E16" s="36">
-        <v>-3.8550219400000002E-2</v>
-      </c>
-      <c r="F16" s="12">
-        <v>-4.0115091399999997E-2</v>
-      </c>
-      <c r="G16" s="26">
-        <v>0.894086979</v>
-      </c>
-      <c r="H16" s="11">
-        <v>-3.4467249200000001E-2</v>
-      </c>
-      <c r="I16" s="26">
-        <v>-3.58663808E-2</v>
-      </c>
-      <c r="J16" s="11">
-        <v>-1.3837476799999999E-3</v>
-      </c>
-      <c r="K16" s="26">
-        <v>3.1211057599999998</v>
-      </c>
-      <c r="L16" s="36">
-        <v>0.24944206199999999</v>
-      </c>
-      <c r="M16" s="12">
-        <v>-0.23971125500000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="22">
-        <v>7</v>
-      </c>
-      <c r="B17" s="30">
-        <v>1.00424307</v>
-      </c>
-      <c r="C17" s="16">
-        <v>1.0042647</v>
-      </c>
-      <c r="D17" s="23">
-        <v>1.8050449799999999E-5</v>
-      </c>
-      <c r="E17" s="30">
-        <v>-0.24944206199999999</v>
-      </c>
-      <c r="F17" s="16">
-        <v>0.23971125500000001</v>
-      </c>
-      <c r="G17" s="23">
-        <v>2.4944899300000001E-3</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-6.2223071099999996E-4</v>
-      </c>
-      <c r="I17" s="23">
-        <v>5.9795731100000004E-4</v>
-      </c>
-      <c r="J17" s="15">
-        <v>-1.4927452899999999E-4</v>
-      </c>
-      <c r="K17" s="23">
-        <v>1.5906761</v>
-      </c>
-      <c r="L17" s="30">
-        <v>4.1599756599999997E-3</v>
-      </c>
-      <c r="M17" s="16">
-        <v>4.3263696400000001E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="63"/>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="63"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="63"/>
-      <c r="N19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="48"/>
-      <c r="M20" s="48"/>
+      <c r="B20" s="46">
+        <v>2.6388842499999998</v>
+      </c>
+      <c r="C20" s="47">
+        <v>1.9533605599999999</v>
+      </c>
+      <c r="D20" s="24">
+        <v>-2.5954843200000002</v>
+      </c>
+      <c r="E20" s="46">
+        <v>0</v>
+      </c>
+      <c r="F20" s="47">
+        <v>5.3301363300000001E-2</v>
+      </c>
+      <c r="G20" s="24">
+        <v>0.26867805500000003</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="24">
+        <v>1.43209067E-2</v>
+      </c>
+      <c r="J20" s="9">
+        <v>-3.8192142899999998E-4</v>
+      </c>
+      <c r="K20" s="24">
+        <v>0.933582472</v>
+      </c>
+      <c r="L20" s="46">
+        <v>2.6147972700000001E-3</v>
+      </c>
+      <c r="M20" s="47">
+        <v>0</v>
+      </c>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="49"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="49"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="40"/>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="20"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="49"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="40"/>
+      <c r="M23" s="40"/>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="61"/>
-      <c r="C24" s="61"/>
-      <c r="D24" s="61"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="61"/>
-      <c r="L24" s="61"/>
-      <c r="M24" s="62"/>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="49"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="57"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="58"/>
-      <c r="G25" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" s="11"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="L25" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="M25" s="58"/>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="20">
-        <v>1</v>
-      </c>
-      <c r="B26" s="29">
-        <v>2.0710685099999999</v>
-      </c>
-      <c r="C26" s="14">
-        <v>4.2928375000000001</v>
-      </c>
-      <c r="D26" s="17">
-        <v>1.1484216700000001</v>
-      </c>
-      <c r="E26" s="29">
-        <v>-42008.010499999997</v>
-      </c>
-      <c r="F26" s="14">
-        <v>4200.00288</v>
-      </c>
-      <c r="G26" s="17">
-        <v>6.9723165900000006E-5</v>
-      </c>
-      <c r="H26" s="13">
-        <v>-2.9289314900000001</v>
-      </c>
-      <c r="I26" s="17">
-        <v>0.292837497</v>
-      </c>
-      <c r="J26" s="13">
-        <v>-44114.851600000002</v>
-      </c>
-      <c r="K26" s="17">
-        <v>1.9206537100000001</v>
-      </c>
-      <c r="L26" s="29">
-        <v>-0.76788308999999999</v>
-      </c>
-      <c r="M26" s="14">
-        <v>0.70254135799999995</v>
-      </c>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N27" s="1"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="1"/>
+    </row>
+    <row r="33" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="60"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="60"/>
+      <c r="L34" s="60"/>
+      <c r="M34" s="61"/>
+    </row>
+    <row r="35" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="56"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="57"/>
+      <c r="G35" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="31"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="31"/>
+      <c r="K35" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="L35" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="M35" s="57"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" s="70">
+        <v>1</v>
+      </c>
+      <c r="B36" s="56">
+        <v>4.4811460500000004</v>
+      </c>
+      <c r="C36" s="57">
+        <v>4.4988980300000003</v>
+      </c>
+      <c r="D36" s="65">
+        <v>12.1498911</v>
+      </c>
+      <c r="E36" s="56">
+        <v>-208.00001700000001</v>
+      </c>
+      <c r="F36" s="57">
+        <v>200.00001700000001</v>
+      </c>
+      <c r="G36" s="65">
+        <v>2.4944899300000001E-3</v>
+      </c>
+      <c r="H36" s="67">
+        <v>-0.51885394799999995</v>
+      </c>
+      <c r="I36" s="65">
+        <v>0.49889802700000002</v>
+      </c>
+      <c r="J36" s="67">
+        <v>-103.850109</v>
+      </c>
+      <c r="K36" s="67">
+        <v>1.5884248400000001</v>
+      </c>
+      <c r="L36" s="32">
+        <v>3.4118965399999999</v>
+      </c>
+      <c r="M36" s="33">
+        <v>3.5503955299999999</v>
+      </c>
+      <c r="N36" s="1"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" s="71"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="75"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="75"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="68"/>
+      <c r="I37" s="64"/>
+      <c r="J37" s="68"/>
+      <c r="K37" s="68"/>
+      <c r="L37" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="M37" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="72"/>
+      <c r="B38" s="74"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="74"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="69"/>
+      <c r="I38" s="66"/>
+      <c r="J38" s="69"/>
+      <c r="K38" s="69"/>
+      <c r="L38" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="M38" s="14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39" s="71">
         <v>2</v>
       </c>
-      <c r="B27" s="36">
-        <v>2.0713442299999998</v>
-      </c>
-      <c r="C27" s="12">
-        <v>4.2925852400000002</v>
-      </c>
-      <c r="D27" s="26">
-        <v>1.1482271900000001</v>
-      </c>
-      <c r="E27" s="36">
-        <v>0.76788308999999999</v>
-      </c>
-      <c r="F27" s="12">
-        <v>-0.70254135799999995</v>
-      </c>
-      <c r="G27" s="26">
-        <v>3.59060426E-4</v>
-      </c>
-      <c r="H27" s="11">
-        <v>2.7571642999999998E-4</v>
-      </c>
-      <c r="I27" s="26">
-        <v>-2.5225479899999999E-4</v>
-      </c>
-      <c r="J27" s="11">
-        <v>-1.9448398500000001E-4</v>
-      </c>
-      <c r="K27" s="26">
-        <v>1.8622040500000001</v>
-      </c>
-      <c r="L27" s="36">
-        <v>0.38758196700000003</v>
-      </c>
-      <c r="M27" s="12">
-        <v>0.42366399300000002</v>
-      </c>
-      <c r="N27" s="1"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="1"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="1"/>
-    </row>
-    <row r="33" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="60" t="s">
+      <c r="B39" s="73">
+        <v>1.3755638800000001</v>
+      </c>
+      <c r="C39" s="75">
+        <v>1.3774790299999999</v>
+      </c>
+      <c r="D39" s="64">
+        <v>0.14141500700000001</v>
+      </c>
+      <c r="E39" s="73">
+        <v>-3.4734569</v>
+      </c>
+      <c r="F39" s="75">
+        <v>-3.49116969</v>
+      </c>
+      <c r="G39" s="64">
+        <v>0.89408973999999997</v>
+      </c>
+      <c r="H39" s="68">
+        <v>-3.1055821699999999</v>
+      </c>
+      <c r="I39" s="64">
+        <v>-3.1214189999999999</v>
+      </c>
+      <c r="J39" s="68">
+        <v>-12.008476099999999</v>
+      </c>
+      <c r="K39" s="67">
+        <v>3.1397450600000001</v>
+      </c>
+      <c r="L39" s="27">
+        <v>0.36809738600000003</v>
+      </c>
+      <c r="M39" s="12">
+        <v>0.38303066299999999</v>
+      </c>
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" s="71"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="75"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="75"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="68"/>
+      <c r="I40" s="64"/>
+      <c r="J40" s="68"/>
+      <c r="K40" s="68"/>
+      <c r="L40" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="M40" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="71"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="64"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="69"/>
+      <c r="L41" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="M41" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N41" s="1"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42" s="70">
+        <v>3</v>
+      </c>
+      <c r="B42" s="56">
+        <v>1.0397276600000001</v>
+      </c>
+      <c r="C42" s="57">
+        <v>1.0399302500000001</v>
+      </c>
+      <c r="D42" s="65">
+        <v>1.5823909799999999E-3</v>
+      </c>
+      <c r="E42" s="56">
+        <v>-0.37556404399999999</v>
+      </c>
+      <c r="F42" s="57">
+        <v>-0.37747919699999999</v>
+      </c>
+      <c r="G42" s="65">
+        <v>0.89421824500000002</v>
+      </c>
+      <c r="H42" s="67">
+        <v>-0.33583622000000002</v>
+      </c>
+      <c r="I42" s="65">
+        <v>-0.33754878500000002</v>
+      </c>
+      <c r="J42" s="67">
+        <v>-0.13983261599999999</v>
+      </c>
+      <c r="K42" s="67">
+        <v>3.1391468599999999</v>
+      </c>
+      <c r="L42" s="32">
+        <v>3.8937854700000003E-2</v>
+      </c>
+      <c r="M42" s="33">
+        <v>4.0517668200000002E-2</v>
+      </c>
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" s="71"/>
+      <c r="B43" s="73"/>
+      <c r="C43" s="75"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="73"/>
+      <c r="F43" s="75"/>
+      <c r="G43" s="64"/>
+      <c r="H43" s="68"/>
+      <c r="I43" s="64"/>
+      <c r="J43" s="68"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="61"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="61"/>
-      <c r="M34" s="62"/>
-    </row>
-    <row r="35" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="43"/>
-      <c r="C35" s="44"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" s="44"/>
-      <c r="G35" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" s="33"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="L35" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="M35" s="44"/>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A36" s="59">
-        <v>1</v>
-      </c>
-      <c r="B36" s="43">
-        <v>4.4811460500000004</v>
-      </c>
-      <c r="C36" s="44">
-        <v>4.4988980300000003</v>
-      </c>
-      <c r="D36" s="56">
-        <v>12.1498911</v>
-      </c>
-      <c r="E36" s="43">
-        <v>-208.00001700000001</v>
-      </c>
-      <c r="F36" s="44">
-        <v>200.00001700000001</v>
-      </c>
-      <c r="G36" s="56">
-        <v>2.4944899300000001E-3</v>
-      </c>
-      <c r="H36" s="53">
-        <v>-0.51885394799999995</v>
-      </c>
-      <c r="I36" s="56">
-        <v>0.49889802700000002</v>
-      </c>
-      <c r="J36" s="53">
-        <v>-103.850109</v>
-      </c>
-      <c r="K36" s="53">
-        <v>1.5884248400000001</v>
-      </c>
-      <c r="L36" s="34">
-        <v>3.4118965399999999</v>
-      </c>
-      <c r="M36" s="35">
-        <v>3.5503955299999999</v>
-      </c>
-      <c r="N36" s="1"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A37" s="46"/>
-      <c r="B37" s="51"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="54"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="54"/>
-      <c r="K37" s="54"/>
-      <c r="L37" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="M37" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="N37" s="1"/>
-    </row>
-    <row r="38" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="47"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="55"/>
-      <c r="L38" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="M38" s="16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A39" s="46">
-        <v>2</v>
-      </c>
-      <c r="B39" s="51">
-        <v>1.3755638800000001</v>
-      </c>
-      <c r="C39" s="50">
-        <v>1.3774790299999999</v>
-      </c>
-      <c r="D39" s="48">
-        <v>0.14141500700000001</v>
-      </c>
-      <c r="E39" s="51">
-        <v>-3.4734569</v>
-      </c>
-      <c r="F39" s="50">
-        <v>-3.49116969</v>
-      </c>
-      <c r="G39" s="48">
-        <v>0.89408973999999997</v>
-      </c>
-      <c r="H39" s="54">
-        <v>-3.1055821699999999</v>
-      </c>
-      <c r="I39" s="48">
-        <v>-3.1214189999999999</v>
-      </c>
-      <c r="J39" s="54">
-        <v>-12.008476099999999</v>
-      </c>
-      <c r="K39" s="53">
-        <v>3.1397450600000001</v>
-      </c>
-      <c r="L39" s="29">
-        <v>0.36809738600000003</v>
-      </c>
-      <c r="M39" s="14">
-        <v>0.38303066299999999</v>
-      </c>
-      <c r="N39" s="1"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A40" s="46"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="54"/>
-      <c r="I40" s="48"/>
-      <c r="J40" s="54"/>
-      <c r="K40" s="54"/>
-      <c r="L40" s="29" t="s">
+      <c r="M43" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N43" s="1"/>
+    </row>
+    <row r="44" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="72"/>
+      <c r="B44" s="74"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="66"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="66"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="66"/>
+      <c r="J44" s="69"/>
+      <c r="K44" s="69"/>
+      <c r="L44" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="M44" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="M40" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="N40" s="1"/>
-    </row>
-    <row r="41" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="46"/>
-      <c r="B41" s="51"/>
-      <c r="C41" s="50"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="54"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="M41" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="N41" s="1"/>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A42" s="59">
-        <v>3</v>
-      </c>
-      <c r="B42" s="43">
-        <v>1.0397276600000001</v>
-      </c>
-      <c r="C42" s="44">
-        <v>1.0399302500000001</v>
-      </c>
-      <c r="D42" s="56">
-        <v>1.5823909799999999E-3</v>
-      </c>
-      <c r="E42" s="43">
-        <v>-0.37556404399999999</v>
-      </c>
-      <c r="F42" s="44">
-        <v>-0.37747919699999999</v>
-      </c>
-      <c r="G42" s="56">
-        <v>0.89421824500000002</v>
-      </c>
-      <c r="H42" s="53">
-        <v>-0.33583622000000002</v>
-      </c>
-      <c r="I42" s="56">
-        <v>-0.33754878500000002</v>
-      </c>
-      <c r="J42" s="53">
-        <v>-0.13983261599999999</v>
-      </c>
-      <c r="K42" s="53">
-        <v>3.1391468599999999</v>
-      </c>
-      <c r="L42" s="34">
-        <v>3.8937854700000003E-2</v>
-      </c>
-      <c r="M42" s="35">
-        <v>4.0517668200000002E-2</v>
-      </c>
-      <c r="N42" s="1"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A43" s="46"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="54"/>
-      <c r="K43" s="54"/>
-      <c r="L43" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="M43" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="N43" s="1"/>
-    </row>
-    <row r="44" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="47"/>
-      <c r="B44" s="52"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="49"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="45"/>
-      <c r="G44" s="49"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="55"/>
-      <c r="K44" s="55"/>
-      <c r="L44" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="M44" s="16" t="s">
-        <v>28</v>
-      </c>
       <c r="N44" s="1"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A45" s="46">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A45" s="71">
         <v>4</v>
       </c>
-      <c r="B45" s="51">
+      <c r="B45" s="73">
         <v>1.0042032700000001</v>
       </c>
-      <c r="C45" s="50">
+      <c r="C45" s="75">
         <v>1.0042247</v>
       </c>
-      <c r="D45" s="48">
+      <c r="D45" s="64">
         <v>1.7713407000000001E-5</v>
       </c>
-      <c r="E45" s="51">
+      <c r="E45" s="73">
         <v>-3.9727756400000001E-2</v>
       </c>
-      <c r="F45" s="50">
+      <c r="F45" s="75">
         <v>-3.9930344700000002E-2</v>
       </c>
-      <c r="G45" s="48">
+      <c r="G45" s="64">
         <v>0.89419571600000003</v>
       </c>
-      <c r="H45" s="54">
+      <c r="H45" s="68">
         <v>-3.5524389500000003E-2</v>
       </c>
-      <c r="I45" s="48">
+      <c r="I45" s="64">
         <v>-3.5705543200000002E-2</v>
       </c>
-      <c r="J45" s="54">
+      <c r="J45" s="68">
         <v>-1.5646775700000001E-3</v>
       </c>
-      <c r="K45" s="53">
+      <c r="K45" s="67">
         <v>3.13906011</v>
       </c>
-      <c r="L45" s="29">
+      <c r="L45" s="27">
         <v>4.1197950699999996E-3</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="12">
         <v>4.2869432299999996E-3</v>
       </c>
       <c r="N45" s="1"/>
@@ -6468,23 +8672,23 @@
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A46" s="46"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="50"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="50"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="54"/>
-      <c r="I46" s="48"/>
-      <c r="J46" s="54"/>
-      <c r="K46" s="54"/>
-      <c r="L46" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="M46" s="14" t="s">
-        <v>27</v>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A46" s="71"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="75"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="75"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="68"/>
+      <c r="I46" s="64"/>
+      <c r="J46" s="68"/>
+      <c r="K46" s="68"/>
+      <c r="L46" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
@@ -6495,23 +8699,23 @@
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
     </row>
-    <row r="47" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="46"/>
-      <c r="B47" s="51"/>
-      <c r="C47" s="50"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="51"/>
-      <c r="F47" s="50"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="54"/>
-      <c r="I47" s="48"/>
-      <c r="J47" s="54"/>
-      <c r="K47" s="55"/>
-      <c r="L47" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="M47" s="14" t="s">
-        <v>26</v>
+    <row r="47" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="71"/>
+      <c r="B47" s="73"/>
+      <c r="C47" s="75"/>
+      <c r="D47" s="64"/>
+      <c r="E47" s="73"/>
+      <c r="F47" s="75"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="68"/>
+      <c r="I47" s="64"/>
+      <c r="J47" s="68"/>
+      <c r="K47" s="69"/>
+      <c r="L47" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
@@ -6522,44 +8726,44 @@
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A48" s="59">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A48" s="70">
         <v>5</v>
       </c>
-      <c r="B48" s="43">
+      <c r="B48" s="56">
         <v>1.0004447000000001</v>
       </c>
-      <c r="C48" s="44">
+      <c r="C48" s="57">
         <v>1.00044697</v>
       </c>
-      <c r="D48" s="56">
+      <c r="D48" s="65">
         <v>1.9827172199999999E-7</v>
       </c>
-      <c r="E48" s="43">
+      <c r="E48" s="56">
         <v>-4.20336883E-3</v>
       </c>
-      <c r="F48" s="44">
+      <c r="F48" s="57">
         <v>-4.2248035399999996E-3</v>
       </c>
-      <c r="G48" s="56">
+      <c r="G48" s="65">
         <v>0.89418015900000003</v>
       </c>
-      <c r="H48" s="53">
+      <c r="H48" s="67">
         <v>-3.7585689999999998E-3</v>
       </c>
-      <c r="I48" s="56">
+      <c r="I48" s="65">
         <v>-3.7777355000000001E-3</v>
       </c>
-      <c r="J48" s="53">
+      <c r="J48" s="67">
         <v>-1.7515135300000002E-5</v>
       </c>
-      <c r="K48" s="53">
+      <c r="K48" s="67">
         <v>3.1390505700000002</v>
       </c>
-      <c r="L48" s="34">
+      <c r="L48" s="32">
         <v>4.35956037E-4</v>
       </c>
-      <c r="M48" s="35">
+      <c r="M48" s="33">
         <v>4.53643637E-4</v>
       </c>
       <c r="N48" s="1"/>
@@ -6571,23 +8775,23 @@
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A49" s="46"/>
-      <c r="B49" s="51"/>
-      <c r="C49" s="50"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="50"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="48"/>
-      <c r="J49" s="54"/>
-      <c r="K49" s="54"/>
-      <c r="L49" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="M49" s="14" t="s">
-        <v>27</v>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A49" s="71"/>
+      <c r="B49" s="73"/>
+      <c r="C49" s="75"/>
+      <c r="D49" s="64"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="75"/>
+      <c r="G49" s="64"/>
+      <c r="H49" s="68"/>
+      <c r="I49" s="64"/>
+      <c r="J49" s="68"/>
+      <c r="K49" s="68"/>
+      <c r="L49" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="M49" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
@@ -6598,23 +8802,23 @@
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
     </row>
-    <row r="50" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="47"/>
-      <c r="B50" s="52"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="45"/>
-      <c r="G50" s="49"/>
-      <c r="H50" s="55"/>
-      <c r="I50" s="49"/>
-      <c r="J50" s="55"/>
-      <c r="K50" s="55"/>
-      <c r="L50" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="M50" s="16" t="s">
-        <v>26</v>
+    <row r="50" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="72"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="58"/>
+      <c r="D50" s="66"/>
+      <c r="E50" s="74"/>
+      <c r="F50" s="58"/>
+      <c r="G50" s="66"/>
+      <c r="H50" s="69"/>
+      <c r="I50" s="66"/>
+      <c r="J50" s="69"/>
+      <c r="K50" s="69"/>
+      <c r="L50" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="M50" s="14" t="s">
+        <v>21</v>
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
@@ -6625,20 +8829,20 @@
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
     </row>
-    <row r="51" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="15"/>
+      <c r="M51" s="15"/>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
@@ -6648,286 +8852,807 @@
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
     </row>
-    <row r="52" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="60" t="s">
-        <v>20</v>
-      </c>
-      <c r="B52" s="61"/>
-      <c r="C52" s="61"/>
-      <c r="D52" s="61"/>
-      <c r="E52" s="61"/>
-      <c r="F52" s="61"/>
-      <c r="G52" s="61"/>
-      <c r="H52" s="61"/>
-      <c r="I52" s="61"/>
-      <c r="J52" s="61"/>
-      <c r="K52" s="61"/>
-      <c r="L52" s="61"/>
-      <c r="M52" s="62"/>
-    </row>
-    <row r="53" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B53" s="57"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="F53" s="58"/>
-      <c r="G53" s="26" t="s">
+    <row r="52" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="H53" s="11"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="L53" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="M53" s="58"/>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A54" s="59">
+      <c r="B52" s="60"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="60"/>
+      <c r="E52" s="60"/>
+      <c r="F52" s="60"/>
+      <c r="G52" s="60"/>
+      <c r="H52" s="60"/>
+      <c r="I52" s="60"/>
+      <c r="J52" s="60"/>
+      <c r="K52" s="60"/>
+      <c r="L52" s="60"/>
+      <c r="M52" s="61"/>
+    </row>
+    <row r="53" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="62"/>
+      <c r="C53" s="63"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" s="63"/>
+      <c r="G53" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="H53" s="9"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="L53" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="M53" s="63"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A54" s="70">
         <v>1</v>
       </c>
-      <c r="B54" s="43">
+      <c r="B54" s="56">
         <v>2.0710685099999999</v>
       </c>
-      <c r="C54" s="44">
+      <c r="C54" s="57">
         <v>4.2928375000000001</v>
       </c>
-      <c r="D54" s="56">
+      <c r="D54" s="65">
         <v>1.1484216700000001</v>
       </c>
-      <c r="E54" s="43">
+      <c r="E54" s="56">
         <v>-42008.010499999997</v>
       </c>
-      <c r="F54" s="44">
+      <c r="F54" s="57">
         <v>4200.00288</v>
       </c>
-      <c r="G54" s="56">
+      <c r="G54" s="65">
         <v>6.9723165900000006E-5</v>
       </c>
-      <c r="H54" s="53">
+      <c r="H54" s="67">
         <v>-2.9289314900000001</v>
       </c>
-      <c r="I54" s="56">
+      <c r="I54" s="65">
         <v>0.292837497</v>
       </c>
-      <c r="J54" s="53">
+      <c r="J54" s="67">
         <v>-44114.851600000002</v>
       </c>
-      <c r="K54" s="56">
+      <c r="K54" s="65">
         <v>1.9206537100000001</v>
       </c>
-      <c r="L54" s="34">
+      <c r="L54" s="32">
         <v>-0.76788308999999999</v>
       </c>
-      <c r="M54" s="35">
+      <c r="M54" s="33">
         <v>0.70254135799999995</v>
       </c>
       <c r="N54" s="1"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
-      <c r="B55" s="51"/>
-      <c r="C55" s="50"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="50"/>
-      <c r="G55" s="48"/>
-      <c r="H55" s="54"/>
-      <c r="I55" s="48"/>
-      <c r="J55" s="54"/>
-      <c r="K55" s="48"/>
-      <c r="L55" s="29" t="s">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A55" s="71"/>
+      <c r="B55" s="73"/>
+      <c r="C55" s="75"/>
+      <c r="D55" s="64"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="75"/>
+      <c r="G55" s="64"/>
+      <c r="H55" s="68"/>
+      <c r="I55" s="64"/>
+      <c r="J55" s="68"/>
+      <c r="K55" s="64"/>
+      <c r="L55" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="72"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="66"/>
+      <c r="E56" s="74"/>
+      <c r="F56" s="58"/>
+      <c r="G56" s="66"/>
+      <c r="H56" s="69"/>
+      <c r="I56" s="66"/>
+      <c r="J56" s="69"/>
+      <c r="K56" s="66"/>
+      <c r="L56" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="M56" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A57" s="71">
+        <v>2</v>
+      </c>
+      <c r="B57" s="73">
+        <v>2.07104629</v>
+      </c>
+      <c r="C57" s="75">
+        <v>4.2926150400000003</v>
+      </c>
+      <c r="D57" s="64">
+        <v>1.1482841500000001</v>
+      </c>
+      <c r="E57" s="73">
+        <v>-6.1895709799999997E-2</v>
+      </c>
+      <c r="F57" s="75">
+        <v>-0.61956688299999996</v>
+      </c>
+      <c r="G57" s="64">
+        <v>3.59060426E-4</v>
+      </c>
+      <c r="H57" s="68">
+        <v>-2.2224299899999998E-5</v>
+      </c>
+      <c r="I57" s="64">
+        <v>-2.22461949E-4</v>
+      </c>
+      <c r="J57" s="68">
+        <v>-1.3752225000000001E-4</v>
+      </c>
+      <c r="K57" s="64">
+        <v>2.7916405499999999</v>
+      </c>
+      <c r="L57" s="27">
+        <v>-0.659865496</v>
+      </c>
+      <c r="M57" s="12">
+        <v>0.67645999899999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A58" s="71"/>
+      <c r="B58" s="73"/>
+      <c r="C58" s="75"/>
+      <c r="D58" s="64"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="75"/>
+      <c r="G58" s="64"/>
+      <c r="H58" s="68"/>
+      <c r="I58" s="64"/>
+      <c r="J58" s="68"/>
+      <c r="K58" s="64"/>
+      <c r="L58" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="M58" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="N58" s="1"/>
+    </row>
+    <row r="59" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="72"/>
+      <c r="B59" s="74"/>
+      <c r="C59" s="58"/>
+      <c r="D59" s="66"/>
+      <c r="E59" s="74"/>
+      <c r="F59" s="58"/>
+      <c r="G59" s="66"/>
+      <c r="H59" s="69"/>
+      <c r="I59" s="66"/>
+      <c r="J59" s="69"/>
+      <c r="K59" s="66"/>
+      <c r="L59" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="M55" s="5" t="s">
+      <c r="M59" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="47"/>
-      <c r="B56" s="52"/>
-      <c r="C56" s="45"/>
-      <c r="D56" s="49"/>
-      <c r="E56" s="52"/>
-      <c r="F56" s="45"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="55"/>
-      <c r="I56" s="49"/>
-      <c r="J56" s="55"/>
-      <c r="K56" s="49"/>
-      <c r="L56" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="M56" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A57" s="46">
+    <row r="60" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="60"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="60"/>
+      <c r="E61" s="60"/>
+      <c r="F61" s="60"/>
+      <c r="G61" s="60"/>
+      <c r="H61" s="60"/>
+      <c r="I61" s="60"/>
+      <c r="J61" s="60"/>
+      <c r="K61" s="60"/>
+      <c r="L61" s="60"/>
+      <c r="M61" s="61"/>
+    </row>
+    <row r="62" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" s="62"/>
+      <c r="C62" s="63"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" s="63"/>
+      <c r="G62" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="H62" s="9"/>
+      <c r="I62" s="24"/>
+      <c r="J62" s="9"/>
+      <c r="K62" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="L62" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="M62" s="63"/>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A63" s="80">
+        <v>1</v>
+      </c>
+      <c r="B63" s="56">
+        <v>2.9999991100000001</v>
+      </c>
+      <c r="C63" s="57">
+        <v>1.93903965</v>
+      </c>
+      <c r="D63" s="67">
+        <v>-2.45849421</v>
+      </c>
+      <c r="E63" s="56">
+        <v>-5.5511151200000002E-8</v>
+      </c>
+      <c r="F63" s="57">
+        <v>0.245254372</v>
+      </c>
+      <c r="G63" s="67">
+        <v>16.0610374</v>
+      </c>
+      <c r="H63" s="67">
+        <v>-8.91566677E-7</v>
+      </c>
+      <c r="I63" s="67">
+        <v>3.9390396499999998</v>
+      </c>
+      <c r="J63" s="67">
+        <v>-2.0906145899999999</v>
+      </c>
+      <c r="K63" s="67">
+        <v>0.99699381600000003</v>
+      </c>
+      <c r="L63" s="43">
+        <v>0.77591000300000001</v>
+      </c>
+      <c r="M63" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A64" s="81"/>
+      <c r="B64" s="73"/>
+      <c r="C64" s="75"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="73"/>
+      <c r="F64" s="75"/>
+      <c r="G64" s="68"/>
+      <c r="H64" s="68"/>
+      <c r="I64" s="68"/>
+      <c r="J64" s="68"/>
+      <c r="K64" s="68"/>
+      <c r="L64" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="M64" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="82"/>
+      <c r="B65" s="74"/>
+      <c r="C65" s="58"/>
+      <c r="D65" s="69"/>
+      <c r="E65" s="74"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="69"/>
+      <c r="H65" s="69"/>
+      <c r="I65" s="69"/>
+      <c r="J65" s="69"/>
+      <c r="K65" s="69"/>
+      <c r="L65" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="M65" s="37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="52">
         <v>2</v>
       </c>
-      <c r="B57" s="51">
-        <v>2.07104629</v>
-      </c>
-      <c r="C57" s="50">
-        <v>4.2926150400000003</v>
-      </c>
-      <c r="D57" s="48">
-        <v>1.1482841500000001</v>
-      </c>
-      <c r="E57" s="51">
-        <v>-6.1895709799999997E-2</v>
-      </c>
-      <c r="F57" s="50">
-        <v>-0.61956688299999996</v>
-      </c>
-      <c r="G57" s="48">
-        <v>3.59060426E-4</v>
-      </c>
-      <c r="H57" s="54">
-        <v>-2.2224299899999998E-5</v>
-      </c>
-      <c r="I57" s="48">
-        <v>-2.22461949E-4</v>
-      </c>
-      <c r="J57" s="54">
-        <v>-1.3752225000000001E-4</v>
-      </c>
-      <c r="K57" s="48">
-        <v>2.7916405499999999</v>
-      </c>
-      <c r="L57" s="29">
-        <v>-0.659865496</v>
-      </c>
-      <c r="M57" s="14">
-        <v>0.67645999899999998</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A58" s="46"/>
-      <c r="B58" s="51"/>
-      <c r="C58" s="50"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="51"/>
-      <c r="F58" s="50"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="54"/>
-      <c r="I58" s="48"/>
-      <c r="J58" s="54"/>
-      <c r="K58" s="48"/>
-      <c r="L58" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="M58" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="N58" s="1"/>
-    </row>
-    <row r="59" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="47"/>
-      <c r="B59" s="52"/>
-      <c r="C59" s="45"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="45"/>
-      <c r="G59" s="49"/>
-      <c r="H59" s="55"/>
-      <c r="I59" s="49"/>
-      <c r="J59" s="55"/>
-      <c r="K59" s="49"/>
-      <c r="L59" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="M59" s="16" t="s">
-        <v>41</v>
+      <c r="B66" s="56">
+        <v>2.6388837299999999</v>
+      </c>
+      <c r="C66" s="57">
+        <v>3.0814997499999999</v>
+      </c>
+      <c r="D66" s="67">
+        <v>-1.10308629</v>
+      </c>
+      <c r="E66" s="56">
+        <v>-0.77591111400000001</v>
+      </c>
+      <c r="F66" s="57">
+        <v>2.4547486699999999</v>
+      </c>
+      <c r="G66" s="67">
+        <v>0.46540817499999998</v>
+      </c>
+      <c r="H66" s="67">
+        <v>-0.36111537599999999</v>
+      </c>
+      <c r="I66" s="67">
+        <v>1.1424601000000001</v>
+      </c>
+      <c r="J66" s="67">
+        <v>1.35540792</v>
+      </c>
+      <c r="K66" s="67">
+        <v>1.01432506</v>
+      </c>
+      <c r="L66" s="35">
+        <v>-0.21259927200000001</v>
+      </c>
+      <c r="M66" s="36">
+        <v>1.46370804</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" s="79"/>
+      <c r="B67" s="73"/>
+      <c r="C67" s="75"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="73"/>
+      <c r="F67" s="75"/>
+      <c r="G67" s="68"/>
+      <c r="H67" s="68"/>
+      <c r="I67" s="68"/>
+      <c r="J67" s="68"/>
+      <c r="K67" s="68"/>
+      <c r="L67" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="M67" s="42" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="53"/>
+      <c r="B68" s="74"/>
+      <c r="C68" s="58"/>
+      <c r="D68" s="69"/>
+      <c r="E68" s="74"/>
+      <c r="F68" s="58"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="69"/>
+      <c r="I68" s="69"/>
+      <c r="J68" s="69"/>
+      <c r="K68" s="69"/>
+      <c r="L68" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="M68" s="37" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="80">
+        <v>3</v>
+      </c>
+      <c r="B69" s="56">
+        <v>2.2294945899999998</v>
+      </c>
+      <c r="C69" s="57">
+        <v>1.8894538700000001</v>
+      </c>
+      <c r="D69" s="67">
+        <v>-2.4556806199999999</v>
+      </c>
+      <c r="E69" s="56">
+        <v>-0.53429604600000002</v>
+      </c>
+      <c r="F69" s="57">
+        <v>-1.5557456999999999</v>
+      </c>
+      <c r="G69" s="67">
+        <v>0.76622155000000003</v>
+      </c>
+      <c r="H69" s="67">
+        <v>-0.40938914399999998</v>
+      </c>
+      <c r="I69" s="67">
+        <v>-1.19204588</v>
+      </c>
+      <c r="J69" s="67">
+        <v>-1.3525943300000001</v>
+      </c>
+      <c r="K69" s="67">
+        <v>2.60463954</v>
+      </c>
+      <c r="L69" s="43">
+        <v>-0.55572657599999997</v>
+      </c>
+      <c r="M69" s="42">
+        <v>-0.33112224099999998</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="81"/>
+      <c r="B70" s="73"/>
+      <c r="C70" s="75"/>
+      <c r="D70" s="68"/>
+      <c r="E70" s="73"/>
+      <c r="F70" s="75"/>
+      <c r="G70" s="68"/>
+      <c r="H70" s="68"/>
+      <c r="I70" s="68"/>
+      <c r="J70" s="68"/>
+      <c r="K70" s="68"/>
+      <c r="L70" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="M70" s="42" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="82"/>
+      <c r="B71" s="74"/>
+      <c r="C71" s="58"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="74"/>
+      <c r="F71" s="58"/>
+      <c r="G71" s="69"/>
+      <c r="H71" s="69"/>
+      <c r="I71" s="69"/>
+      <c r="J71" s="69"/>
+      <c r="K71" s="69"/>
+      <c r="L71" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="M71" s="37" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" s="52">
+        <v>4</v>
+      </c>
+      <c r="B72" s="56">
+        <v>2.48213442</v>
+      </c>
+      <c r="C72" s="57">
+        <v>2.0122848200000001</v>
+      </c>
+      <c r="D72" s="67">
+        <v>-2.5692670999999998</v>
+      </c>
+      <c r="E72" s="56">
+        <v>0.51179795299999997</v>
+      </c>
+      <c r="F72" s="57">
+        <v>0.24883103600000001</v>
+      </c>
+      <c r="G72" s="67">
+        <v>0.493631975</v>
+      </c>
+      <c r="H72" s="67">
+        <v>0.25263983499999998</v>
+      </c>
+      <c r="I72" s="67">
+        <v>0.12283095600000001</v>
+      </c>
+      <c r="J72" s="67">
+        <v>-0.11358647600000001</v>
+      </c>
+      <c r="K72" s="67">
+        <v>0.22869716700000001</v>
+      </c>
+      <c r="L72" s="35">
+        <v>-0.25200552799999998</v>
+      </c>
+      <c r="M72" s="36">
+        <v>0.199880112</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" s="79"/>
+      <c r="B73" s="73"/>
+      <c r="C73" s="75"/>
+      <c r="D73" s="68"/>
+      <c r="E73" s="73"/>
+      <c r="F73" s="75"/>
+      <c r="G73" s="68"/>
+      <c r="H73" s="68"/>
+      <c r="I73" s="68"/>
+      <c r="J73" s="68"/>
+      <c r="K73" s="68"/>
+      <c r="L73" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="M73" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="53"/>
+      <c r="B74" s="74"/>
+      <c r="C74" s="58"/>
+      <c r="D74" s="69"/>
+      <c r="E74" s="74"/>
+      <c r="F74" s="58"/>
+      <c r="G74" s="69"/>
+      <c r="H74" s="69"/>
+      <c r="I74" s="69"/>
+      <c r="J74" s="69"/>
+      <c r="K74" s="69"/>
+      <c r="L74" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M74" s="37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="80">
+        <v>5</v>
+      </c>
+      <c r="B75" s="56">
+        <v>2.6266678400000001</v>
+      </c>
+      <c r="C75" s="57">
+        <v>1.9615809399999999</v>
+      </c>
+      <c r="D75" s="67">
+        <v>-2.5952671199999999</v>
+      </c>
+      <c r="E75" s="56">
+        <v>0.33306603200000001</v>
+      </c>
+      <c r="F75" s="57">
+        <v>-0.116843163</v>
+      </c>
+      <c r="G75" s="67">
+        <v>0.43394822799999999</v>
+      </c>
+      <c r="H75" s="67">
+        <v>0.144533414</v>
+      </c>
+      <c r="I75" s="67">
+        <v>-5.0703883700000001E-2</v>
+      </c>
+      <c r="J75" s="67">
+        <v>-2.6000023399999999E-2</v>
+      </c>
+      <c r="K75" s="67">
+        <v>0.97884335200000006</v>
+      </c>
+      <c r="L75" s="43">
+        <v>-1.8877788199999999E-2</v>
+      </c>
+      <c r="M75" s="42">
+        <v>2.8634872299999999E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" s="81"/>
+      <c r="B76" s="73"/>
+      <c r="C76" s="75"/>
+      <c r="D76" s="68"/>
+      <c r="E76" s="73"/>
+      <c r="F76" s="75"/>
+      <c r="G76" s="68"/>
+      <c r="H76" s="68"/>
+      <c r="I76" s="68"/>
+      <c r="J76" s="68"/>
+      <c r="K76" s="68"/>
+      <c r="L76" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="M76" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="82"/>
+      <c r="B77" s="74"/>
+      <c r="C77" s="58"/>
+      <c r="D77" s="69"/>
+      <c r="E77" s="74"/>
+      <c r="F77" s="58"/>
+      <c r="G77" s="69"/>
+      <c r="H77" s="69"/>
+      <c r="I77" s="69"/>
+      <c r="J77" s="69"/>
+      <c r="K77" s="69"/>
+      <c r="L77" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="M77" s="37" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" s="80">
+        <v>6</v>
+      </c>
+      <c r="B78" s="56">
+        <v>2.6306004999999999</v>
+      </c>
+      <c r="C78" s="57">
+        <v>1.9588374399999999</v>
+      </c>
+      <c r="D78" s="67">
+        <v>-2.5953932399999999</v>
+      </c>
+      <c r="E78" s="56">
+        <v>1.1856123600000001E-2</v>
+      </c>
+      <c r="F78" s="57">
+        <v>-8.2710569299999995E-3</v>
+      </c>
+      <c r="G78" s="67">
+        <v>0.331698993</v>
+      </c>
+      <c r="H78" s="67">
+        <v>3.9326642499999996E-3</v>
+      </c>
+      <c r="I78" s="67">
+        <v>-2.74350126E-3</v>
+      </c>
+      <c r="J78" s="67">
+        <v>-1.26123167E-4</v>
+      </c>
+      <c r="K78" s="67">
+        <v>1.2491848999999999</v>
+      </c>
+      <c r="L78" s="43">
+        <v>-1.2010836800000001E-2</v>
+      </c>
+      <c r="M78" s="42">
+        <v>1.90274463E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" s="81"/>
+      <c r="B79" s="73"/>
+      <c r="C79" s="75"/>
+      <c r="D79" s="68"/>
+      <c r="E79" s="73"/>
+      <c r="F79" s="75"/>
+      <c r="G79" s="68"/>
+      <c r="H79" s="68"/>
+      <c r="I79" s="68"/>
+      <c r="J79" s="68"/>
+      <c r="K79" s="68"/>
+      <c r="L79" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="M79" s="42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="82"/>
+      <c r="B80" s="74"/>
+      <c r="C80" s="58"/>
+      <c r="D80" s="69"/>
+      <c r="E80" s="74"/>
+      <c r="F80" s="58"/>
+      <c r="G80" s="69"/>
+      <c r="H80" s="69"/>
+      <c r="I80" s="69"/>
+      <c r="J80" s="69"/>
+      <c r="K80" s="69"/>
+      <c r="L80" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="M80" s="37" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="101">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="H36:H38"/>
-    <mergeCell ref="I36:I38"/>
-    <mergeCell ref="J36:J38"/>
-    <mergeCell ref="J39:J41"/>
-    <mergeCell ref="J42:J44"/>
-    <mergeCell ref="A34:M34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="F36:F38"/>
-    <mergeCell ref="J45:J47"/>
-    <mergeCell ref="I39:I41"/>
-    <mergeCell ref="H39:H41"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="F39:F41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="H42:H44"/>
-    <mergeCell ref="I42:I44"/>
-    <mergeCell ref="I45:I47"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="D48:D50"/>
-    <mergeCell ref="E48:E50"/>
-    <mergeCell ref="F48:F50"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="K36:K38"/>
-    <mergeCell ref="K39:K41"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="K45:K47"/>
-    <mergeCell ref="K48:K50"/>
-    <mergeCell ref="A52:M52"/>
-    <mergeCell ref="H45:H47"/>
-    <mergeCell ref="G45:G47"/>
-    <mergeCell ref="F45:F47"/>
-    <mergeCell ref="E45:E47"/>
-    <mergeCell ref="D45:D47"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G48:G50"/>
-    <mergeCell ref="H48:H50"/>
-    <mergeCell ref="I48:I50"/>
-    <mergeCell ref="J48:J50"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B48:B50"/>
+  <mergeCells count="167">
+    <mergeCell ref="F75:F77"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="K78:K80"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A69:A71"/>
+    <mergeCell ref="A75:A77"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="D63:D65"/>
+    <mergeCell ref="E63:E65"/>
+    <mergeCell ref="F63:F65"/>
+    <mergeCell ref="G63:G65"/>
+    <mergeCell ref="H63:H65"/>
+    <mergeCell ref="I63:I65"/>
+    <mergeCell ref="J63:J65"/>
+    <mergeCell ref="K63:K65"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="C69:C71"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="C75:C77"/>
+    <mergeCell ref="D69:D71"/>
+    <mergeCell ref="D75:D77"/>
+    <mergeCell ref="E69:E71"/>
+    <mergeCell ref="F69:F71"/>
+    <mergeCell ref="E75:E77"/>
+    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="C78:C80"/>
+    <mergeCell ref="D78:D80"/>
+    <mergeCell ref="E78:E80"/>
+    <mergeCell ref="F78:F80"/>
+    <mergeCell ref="G78:G80"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="I78:I80"/>
+    <mergeCell ref="J72:J74"/>
+    <mergeCell ref="K72:K74"/>
+    <mergeCell ref="G75:G77"/>
+    <mergeCell ref="H75:H77"/>
+    <mergeCell ref="I75:I77"/>
+    <mergeCell ref="J75:J77"/>
+    <mergeCell ref="K75:K77"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="C72:C74"/>
+    <mergeCell ref="D72:D74"/>
+    <mergeCell ref="E72:E74"/>
+    <mergeCell ref="F72:F74"/>
+    <mergeCell ref="G72:G74"/>
+    <mergeCell ref="H72:H74"/>
+    <mergeCell ref="I72:I74"/>
+    <mergeCell ref="J66:J68"/>
+    <mergeCell ref="K66:K68"/>
+    <mergeCell ref="G69:G71"/>
+    <mergeCell ref="H69:H71"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="J69:J71"/>
+    <mergeCell ref="K69:K71"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="B66:B68"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="D66:D68"/>
+    <mergeCell ref="E66:E68"/>
+    <mergeCell ref="F66:F68"/>
+    <mergeCell ref="G66:G68"/>
+    <mergeCell ref="H66:H68"/>
+    <mergeCell ref="I66:I68"/>
+    <mergeCell ref="A61:M61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="E57:E59"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="H54:H56"/>
+    <mergeCell ref="I54:I56"/>
+    <mergeCell ref="A54:A56"/>
     <mergeCell ref="J54:J56"/>
     <mergeCell ref="K54:K56"/>
     <mergeCell ref="K57:K59"/>
@@ -6943,16 +9668,78 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="F54:F56"/>
     <mergeCell ref="G54:G56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="G57:G59"/>
-    <mergeCell ref="F57:F59"/>
-    <mergeCell ref="E57:E59"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="H54:H56"/>
-    <mergeCell ref="I54:I56"/>
-    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="K45:K47"/>
+    <mergeCell ref="K48:K50"/>
+    <mergeCell ref="A52:M52"/>
+    <mergeCell ref="H45:H47"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="F45:F47"/>
+    <mergeCell ref="E45:E47"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="H48:H50"/>
+    <mergeCell ref="I48:I50"/>
+    <mergeCell ref="J48:J50"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="E48:E50"/>
+    <mergeCell ref="F48:F50"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="J45:J47"/>
+    <mergeCell ref="I39:I41"/>
+    <mergeCell ref="H39:H41"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="H42:H44"/>
+    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="I45:I47"/>
+    <mergeCell ref="J39:J41"/>
+    <mergeCell ref="J42:J44"/>
+    <mergeCell ref="A34:M34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="K36:K38"/>
+    <mergeCell ref="K39:K41"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="H36:H38"/>
+    <mergeCell ref="I36:I38"/>
+    <mergeCell ref="J36:J38"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="L2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
